--- a/database/DefinicaoCampos - Copia.xlsx
+++ b/database/DefinicaoCampos - Copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SuperCRM\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234ECB3E-C93D-4FDA-AF68-BECEF0325110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358A4B89-BCA4-4658-9FB6-00F405DDEC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7842B42A-80A9-4B36-ADEF-5A4F17B0DFD4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="43">
   <si>
     <t>Nome Original da Coluna</t>
   </si>
@@ -131,7 +131,40 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Decimal</t>
+    <t>Tabela</t>
+  </si>
+  <si>
+    <t>Proposal</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Decimal (18,2)</t>
+  </si>
+  <si>
+    <t>CustomerRecipient</t>
+  </si>
+  <si>
+    <t>ProposalTypeName</t>
+  </si>
+  <si>
+    <t>Chave Primária</t>
+  </si>
+  <si>
+    <t>ProposalDetail</t>
+  </si>
+  <si>
+    <t>ChaveEstrangeira</t>
+  </si>
+  <si>
+    <t>Proposal.Business Proposal ID</t>
   </si>
 </sst>
 </file>
@@ -175,9 +208,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -518,279 +550,528 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{726463BF-C24B-4C13-990F-3931E4B319DE}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29" style="2" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="C25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" t="s">
-        <v>29</v>
+      <c r="C31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E25">
+    <sortCondition ref="A2:A25"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>